--- a/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
+++ b/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
@@ -10488,12 +10488,16 @@
           <t>Huruf ditarik memanjang seperti karet lalu memantul kembali.</t>
         </is>
       </c>
-      <c r="E13" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>TY12</t>
+        </is>
+      </c>
       <c r="G13" s="9" t="n">
         <v>2</v>
       </c>
@@ -18635,12 +18639,16 @@
           <t>Garis waktu horizontal dengan batang tahapan yang terisi.</t>
         </is>
       </c>
-      <c r="E80" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F80" s="19" t="inlineStr"/>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="inlineStr">
+        <is>
+          <t>GB23</t>
+        </is>
+      </c>
       <c r="G80" s="19" t="n">
         <v>1</v>
       </c>
@@ -26606,12 +26614,16 @@
           <t>Daftar email; satu subjek membuat semua berhenti.</t>
         </is>
       </c>
-      <c r="E147" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F147" s="9" t="inlineStr"/>
+      <c r="E147" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F147" s="9" t="inlineStr">
+        <is>
+          <t>UI10</t>
+        </is>
+      </c>
       <c r="G147" s="9" t="n">
         <v>2</v>
       </c>
@@ -30430,12 +30442,16 @@
           <t>Kolom karakter jatuh seperti hujan di layar gelap.</t>
         </is>
       </c>
-      <c r="E179" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F179" s="9" t="inlineStr"/>
+      <c r="E179" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>SN14</t>
+        </is>
+      </c>
       <c r="G179" s="9" t="n">
         <v>2</v>
       </c>
@@ -33195,12 +33211,16 @@
           <t>Kotak dialog di bawah, pilihan jawaban, latar ruangan.</t>
         </is>
       </c>
-      <c r="E202" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F202" s="19" t="inlineStr"/>
+      <c r="E202" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F202" s="19" t="inlineStr">
+        <is>
+          <t>PF14</t>
+        </is>
+      </c>
       <c r="G202" s="19" t="n">
         <v>2</v>
       </c>

--- a/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
+++ b/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
@@ -22084,12 +22084,16 @@
           <t>Mata rantai tersambung; satu mata retak.</t>
         </is>
       </c>
-      <c r="E109" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F109" s="9" t="inlineStr"/>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="inlineStr">
+        <is>
+          <t>GB52</t>
+        </is>
+      </c>
       <c r="G109" s="9" t="n">
         <v>2</v>
       </c>

--- a/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
+++ b/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
@@ -20660,12 +20660,16 @@
           <t>Jarum meter bergerak dari merah ke hijau.</t>
         </is>
       </c>
-      <c r="E97" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="inlineStr"/>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>GB40</t>
+        </is>
+      </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>

--- a/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
+++ b/rancangan/Rancangan-Iklan-Video-Privasimu.xlsx
@@ -35393,12 +35393,16 @@
           <t>Benda di etalase dengan kartu keterangan museum.</t>
         </is>
       </c>
-      <c r="E220" s="28" t="inlineStr">
-        <is>
-          <t>Bisa</t>
-        </is>
-      </c>
-      <c r="F220" s="19" t="inlineStr"/>
+      <c r="E220" s="22" t="inlineStr">
+        <is>
+          <t>Sudah</t>
+        </is>
+      </c>
+      <c r="F220" s="19" t="inlineStr">
+        <is>
+          <t>PF32</t>
+        </is>
+      </c>
       <c r="G220" s="19" t="n">
         <v>2</v>
       </c>
